--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0035.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0035.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Milestones</t>
+          <t>Cột Mốc</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Theo dấu Kẻ địch</t>
+          <t>Theo Dõi Kẻ Địch</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Path of Growth</t>
+          <t>Con Đường Trưởng Thành</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Recurring Challenges</t>
+          <t>Thử Thách Lặp Lại</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Hoạt Động</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Materials Spots</t>
+          <t>Điểm Thu Thập Vật Liệu</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Sổ tay</t>
+          <t>Sổ Hướng Dẫn</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Companion Stories</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Công cụ</t>
+          <t>Tiện ích</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Crafting</t>
+          <t>Đang chế tác</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Obsolete</t>
+          <t>Lỗi Thời</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Podcast Pioneer</t>
+          <t>Podcast Tiên Phong</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Sonoro Sphere: Weapons</t>
+          <t>Sonoro Sphere: Vũ Khí</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Sonoro Sphere: Skills</t>
+          <t>Khối Sonoro: Kỹ Năng</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Resonance Conversion</t>
+          <t>Chuyển Hóa Cộng Hưởng</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Calamity</t>
+          <t>Bản Hologram Chiến Thuật: Đại Họa</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Thử thách Boss</t>
+          <t>Thử Thách Trùm</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Trò Chơi Thẻ</t>
+          <t>Trò chơi Thẻ</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Trang trí tiệc</t>
+          <t>Trang trí nhóm</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Cuốn Sách Những Khoảnh Khắc</t>
+          <t>Bộ Sưu Tập Những Khoảnh Khắc</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Album Lollo Joy</t>
+          <t>Bộ Sưu Tập Niềm Vui Lollo</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Milestones</t>
+          <t>Cột Mốc</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Thu thập Echo hiếm</t>
+          <t>Thu thập Tiếng Vọng Hiếm</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Đối đầu với các Tacet Discord mạnh mẽ</t>
+          <t>Đối đầu với những Tacet Discord mạnh mẽ</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Growth</t>
+          <t>Sinh Trưởng</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Bước vào thế giới chưa biết</t>
+          <t>Bước vào nơi chưa ai biết tới.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Recurring Challenges</t>
+          <t>Thử Thách Lặp Lại</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Xem cuộc sống thường ngày của Resonators</t>
+          <t>Hãy xem cuộc sống thường nhật của các Resonator đi</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Hướng Dẫn</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Hướng Dẫn</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Adventure</t>
+          <t>Phiêu lưu</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Speciality</t>
+          <t>Đặc sản</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Triệu Tập 10 lần</t>
+          <t>Triệu tập 10 lần</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Chấp Nhận</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Play/Stop</t>
+          <t>Phát/Dừng</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Quay lại</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Switch Resonator</t>
+          <t>Chuyển Resonator</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Trò Chuyện</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Xem Tiền tệ</t>
+          <t>Xem Tiền Tệ</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Xem Vật phẩm</t>
+          <t>Xem Vật Phẩm</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Shortcut List</t>
+          <t>Danh sách Đường tắt</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Xác nhận Option</t>
+          <t>Xác nhận Lựa chọn</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Sao Chép ID</t>
+          <t>Sao chép ID</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Delete</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Next Node</t>
+          <t>Nút Tiếp Theo</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Previous Node</t>
+          <t>Nút trước</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Emote/Action</t>
+          <t>Biểu cảm/Hành động</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>(Giữ) Quit Game</t>
+          <t>(Giữ) Thoát Game</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Bộ lọc</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Nguồn Cội</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Expand/Collapse</t>
+          <t>Mở rộng/Thu gọn</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Hide Source</t>
+          <t>Ẩn Nguồn</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Increase</t>
+          <t>Tăng</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Tham gia Hợp tác</t>
+          <t>Tham Gia Hợp Tác</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Khóa</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Cấp độ Proficiency</t>
+          <t>Cấp độ Thành thạo</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Hướng Camera</t>
+          <t>Điều khiển máy quay</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Triệu Tập Once</t>
+          <t>Triệu tập 1 lần</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Next Page</t>
+          <t>Trang Tiếp Theo</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Previous Page</t>
+          <t>Trang trước</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Tăng cường</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Đọc</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Decrease</t>
+          <t>Giảm</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Từ Chối</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Current Location</t>
+          <t>Vị Trí Hiện Tại</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>(Giữ) Đặt lại Filter</t>
+          <t>(Giữ) Đặt lại bộ lọc</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Đặt lại Camera</t>
+          <t>Đặt lại góc quay</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Character Tiếp Theo</t>
+          <t>Nhân vật tiếp theo</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Lưu</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Chọn Left</t>
+          <t>Chọn bên trái</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Chọn Right</t>
+          <t>Chọn Bên Phải</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Chọn Combat Members</t>
+          <t>Chọn Thành Viên Chiến Đấu</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Item in Details</t>
+          <t>Thông tin chi tiết vật phẩm</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Hoàn tất</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Shoot</t>
+          <t>Bắn</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Theo dõi</t>
+          <t>Bản nhạc</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Nâng cấp/Activate</t>
+          <t>Nâng cấp/Kích hoạt</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Bỏ qua</t>
+          <t>Bỏ Qua</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Autoplay</t>
+          <t>Tự Động Chơi</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Stop Autoplay</t>
+          <t>Dừng Tự Động Phát</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Hide UI</t>
+          <t>Ẩn Giao Diện</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Xem chi tiết</t>
+          <t>Xem Chi Tiết</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Phantom Appearance</t>
+          <t>Hiện Hình Ảo Ảnh</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>View/Thu thập</t>
+          <t>Xem/Nhận</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Quit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>Vào</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>(Long Press) Skip</t>
+          <t>(Giữ lâu) Bỏ qua</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Giai đoạn SOL3</t>
+          <t>Giai Đoạn SOL3</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Không Healthy Game Server Nodes</t>
+          <t>Không có nút máy chủ trò chơi khả dụng</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Phần Thưởng Pioneer Association Huanglong</t>
+          <t>Phần Thưởng Hiệp Hội Tiên Phong Huanglong</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Tất cả Tunings Completed</t>
+          <t>Tất cả các điều chỉnh đã hoàn tất</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Material Tuning</t>
+          <t>Vật Liệu Điều Chỉnh</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ</t>
+          <t>Nguyên liệu không đủ.</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Insufficent Shell Credit</t>
+          <t>Không đủ Shell Credit Sò</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Tuning Successful</t>
+          <t>Điều Chỉnh Thành Công</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Tuning</t>
+          <t>Điều Chỉnh</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Random Force</t>
+          <t>Lực lượng Ngẫu Nhiên</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Huanglong Division</t>
+          <t>Bộ Huanglong</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Huanglong Division</t>
+          <t>Bộ Huanglong</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Lollo Logistics</t>
+          <t>Lollo Hậu Cần</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Cruising Drake</t>
+          <t>Drake Tuần Tiễu</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Exiles - Boar Gang</t>
+          <t>Những Kẻ Lưu Đày - Bang Heo Rừng</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Resonator EXP</t>
+          <t>Kinh nghiệm Resonator</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Weapon EXP</t>
+          <t>Kinh Nghiệm Vũ Khí</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Echo EXP</t>
+          <t>Điểm Kinh Nghiệm Cộng Hưởng</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Echo Set</t>
+          <t>Bộ Âm Hưởng</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Resonance Skill Giả trong Mô phỏng</t>
+          <t>Kỹ năng Resonator trong Mô phỏng</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Bạn nên ưu tiên khám phá lối vào này</t>
+          <t>Bạn nên ưu tiên khám phá lối vào này trước</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Refreshes in:</t>
+          <t>Làm mới sau:</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Đăng nhập vào trò chơi</t>
+          <t>Đăng nhập vào game</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Complete 1 Daily Quest</t>
+          <t>Hoàn thành 1 Nhiệm Vụ Hằng Ngày</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Complete Simulation Challenge 1 time</t>
+          <t>Hoàn thành Thử Thách Mô Phỏng 1 lần</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách Rèn luyện 1 lần</t>
+          <t>Hoàn thành Thử Thách Giả Mạo 1 lần</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách Tacet Field 1 lần</t>
+          <t>Hoàn thành Thử Thách Tổ Tacet 1 lần.</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp độ Echo 1 lần</t>
+          <t>Nâng cấp Cấp Độ Echo một lần</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Tune 1 Echo</t>
+          <t>Điệu nhạc 1 Echo</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp độ Weapon 1 lần</t>
+          <t>Nâng cấp Vũ Khí một lần</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Complete Synthesis once</t>
+          <t>Hoàn thành Tổng Hợp một lần.</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Hoàn thành Cooking 1 lần</t>
+          <t>Hoàn thành Nấu ăn 1 lần</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Complete Crafting once</t>
+          <t>Hoàn thành Chế tạo 1 lần</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Sử dụng 1 Vật phẩm Cung ứng</t>
+          <t>Sử dụng 1 Đồ Tiếp Tế</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Dodge hoặc Counterattack thành công 1 lần</t>
+          <t>Né tránh hoặc Phản công thành công một lần</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp độ Resonator 1 lần</t>
+          <t>Nâng Cấp Cấp Độ Resonator một lần</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Waveworn Phenomenon</t>
+          <t>Hiện Tượng Sóng Mòn</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>"The Lament"</t>
+          <t>"Khúc Bi Ca"</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Discord</t>
+          <t>Tacet Discord</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Threnodian</t>
+          <t>Người Threnody</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Reverberation</t>
+          <t>Sự Giao Thoa Âm Thanh</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Remnant</t>
+          <t>Tàn Tích</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Black Shores: Surface</t>
+          <t>Bờ Biển Đen: Bề Mặt</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Black Shores: Surface</t>
+          <t>Bờ Biển Đen: Bề Mặt</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Black Shores: Surface</t>
+          <t>Bờ Biển Đen: Bề Mặt</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Black Shores: Surface</t>
+          <t>Bờ Biển Đen: Bề Mặt</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Black Shores: Surface</t>
+          <t>Bờ Biển Đen: Bề Mặt</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Black Shores: Underground</t>
+          <t>Bờ Biển Đen: Dưới Lòng Đất</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Black Shores: Underground</t>
+          <t>Bờ Biển Đen: Dưới Lòng Đất</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Black Shores: Underground</t>
+          <t>Bờ Biển Đen: Dưới Lòng Đất</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Black Shores: Underground</t>
+          <t>Bờ Biển Đen: Dưới Lòng Đất</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Black Shores: Underground</t>
+          <t>Bờ Biển Đen: Dưới Lòng Đất</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Mt. Firmament: Hongzhen</t>
+          <t>Núi Firmament: Hongzhen</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Mt. Firmament: Mianloong Chamber</t>
+          <t>Núi Firmament: Mianloong Chamber</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Mt. Firmament: Mianloong Chamber</t>
+          <t>Núi Firmament: Mianloong Chamber</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Prophecy of the Endtimes</t>
+          <t>Lời Tiên Tri Tận Thế</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Doom of Destruction</t>
+          <t>Hủy Diệt Định Mệnh</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>End of Wandering</t>
+          <t>Chấm dứt Lang thang</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Ragunna City</t>
+          <t>Thành Phố Ragunna</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Giáo Đoàn Vực Sâu</t>
+          <t>Lệnh của Vực Sâu</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Silver Moon Grove</t>
+          <t>Lâm Nguyệt Bạc</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Fagaceae Peninsula</t>
+          <t>Bán Đảo Fagaceae</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Penitent's End: Fool's Elysium</t>
+          <t>Hồi Kết của Kẻ Ăn Năn: Thiên Đường của Kẻ Ngốc</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Penitent's End</t>
+          <t>Kết Cục Của Kẻ Ăn Năn</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Averardo Vault: Echo Station</t>
+          <t>Hầm Averardo: Echo Station</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Averardo Vault: Echo Depository</t>
+          <t>Hầm Averardo: Echo Depository</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Averardo Vault: Artworks Depository</t>
+          <t>Hầm Averardo: Kho Tàng Nghệ Thuật</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Averardo Vault: Deeper Area</t>
+          <t>Hầm Averardo: Khu Vực Sâu Hơn</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Riccioli Islands</t>
+          <t>Quần Đảo Riccioli</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Avinoleum: Inverted Seminary</t>
+          <t>Avinoleum: Học Viện Đảo Ngược</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Avinoleum: Tower of Salvation</t>
+          <t>Avinoleum: Tháp Cứu Rỗi</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Avinoleum: Path of Bestowal</t>
+          <t>Avinoleum: Con Đường Ban Phước</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Avinoleum: Zargon Garden</t>
+          <t>Avinoleum: Vườn Zargon</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Simulation Training</t>
+          <t>Huấn Luyện Mô Phỏng</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Thử thách Rèn luyện</t>
+          <t>Thử Thách Giả Tạo</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Challenge Giả Mạo</t>
+          <t>Thử Thách Giả Tạo</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Simulation Challenge</t>
+          <t>Thử Thách Mô Phỏng</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Simulation Challenge</t>
+          <t>Thử Thách Mô Phỏng</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Statue of the Crownless: Heart</t>
+          <t>Tượng Vô Vương: Trái Tim</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Sa Đọa Suy Vong</t>
+          <t>Sự Suy Đồi Tội Lỗi</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Đại Sảnh Trial</t>
+          <t>Đại Sảnh Thử Thách</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Challenge Giả Mạo</t>
+          <t>Thử Thách Giả Tạo</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Challenge Giả Mạo</t>
+          <t>Thử Thách Giả Tạo</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Thử Thách Hàng Tuần: Đại Kết Cục Đỏ Thẫm</t>
+          <t>Thử Thách Hàng Tuần: Chung Cục Đẫm Máu</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Đồi Hoàng Hôn</t>
+          <t>Thăng Bình Hoàng Hôn</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Đồi Tiếng Vang</t>
+          <t>Sự Trỗi Dậy Vang Dội</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Cathedral of Mercury</t>
+          <t>Nhà Thờ Mercury</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Đồi Chỉ Huy</t>
+          <t>Lệnh Triệu Hồi</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Final Stage: Crimson Finale</t>
+          <t>Giai Đoạn Cuối: Đại Kết Đỏ Thẫm</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>"Perfect Trade"</t>
+          <t>"Giao Dịch Hoàn Hảo"</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Cõi Bản Ngã: Mirrors in the Mirror</t>
+          <t>Thế Giới Ảo Tưởng: Những Tấm Gương Trong Gương</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>The Prisoned Song</t>
+          <t>Bài Ca Bị Giam Cầm</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Averardo Vault: Vault Depths</t>
+          <t>Hầm Averardo: Vực Sâu Hầm Ngục</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Vùng Đất Than Thở</t>
+          <t>Vùng Đất Than Khóc</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Weekly Challenge: Broken Fortune</t>
+          <t>Thử thách Hàng tuần: Vận Mệnh Tan Vỡ</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Lake of Spirits</t>
+          <t>Hồ Linh Hồn</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Night Tưởng Niệm</t>
+          <t>Đêm Tưởng Niệm</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Somnoire, Illusive Realm</t>
+          <t>Somnoire, Cõi Ảo Mộng</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Territory Uncharted</t>
+          <t>Vùng Đất Chưa Khám Phá</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Territory Uncharted</t>
+          <t>Vùng Đất Chưa Khám Phá</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Territory Uncharted</t>
+          <t>Vùng Đất Chưa Khám Phá</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Calamity</t>
+          <t>Tai Họa</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Phantom Pain</t>
+          <t>Nỗi Đau Ảo Giác</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Synchronization</t>
+          <t>Đồng Bộ Hóa</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Cấp độ Resonator trung bình hiện tại thấp hơn mức khuyến nghị</t>
+          <t>Cấp độ trung bình của Resonator hiện tại thấp hơn mức khuyến nghị</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Thời gian hoàn thành</t>
+          <t>Xóa bỏ Thời Gian</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Sounds</t>
+          <t>Âm thanh</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Graphics</t>
+          <t>Đồ họa</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Ngôn Ngữ</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Lối chơi</t>
+          <t>Chơi</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Account</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Main Echo not equipped</t>
+          <t>Chưa trang bị Tiếng Vọng Chính</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Broadblade</t>
+          <t>Kiếm Rộng</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Pistols</t>
+          <t>Súng lục</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Gauntlets</t>
+          <t>Bao Tay Chiến Đấu</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Rectifier</t>
+          <t>Bộ điều chỉnh</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Fusion</t>
+          <t>Hợp Nhất</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Exploration type</t>
+          <t>Loại hình thám hiểm</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Loại Combat</t>
+          <t>Loại hình chiến đấu</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Passive type</t>
+          <t>Loại thụ động</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Combat Camera Distance</t>
+          <t>Khoảng Cách Góc Nhìn Chiến Đấu</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Camera Đặt lại</t>
+          <t>Đặt lại máy quay</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Moving Camera Correction</t>
+          <t>Điều Chỉnh Góc Máy Di Chuyển</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Combat Camera Correction</t>
+          <t>Điều Chỉnh Góc Nhìn Chiến Đấu</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Walk-Run Threshold</t>
+          <t>Ngưỡng Chuyển Đổi Đi/Chạy</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Log Upload</t>
+          <t>Tải nhật ký lên</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Joystick Mode</t>
+          <t>Chế Độ Tay Cầm</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Tự Động Switch Sang Giao Diện Combat</t>
+          <t>Tự Động Chuyển Sang Giao Diện Chiến Đấu</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Di chuyển sang phải</t>
+          <t>Phải</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Redemption Code</t>
+          <t>Mã đổi thưởng</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>User Center</t>
+          <t>Trung Tâm Người Dùng</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Điều khoản Sử dụng</t>
+          <t>Điều Khoản Sử Dụng</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Chính sách Bảo mật</t>
+          <t>Chính Sách Bảo Mật</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Children's Privacy Policy</t>
+          <t>Chính Sách Bảo Mật Dành Cho Trẻ Em</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Third-party Information Sharing List</t>
+          <t>Danh sách chia sẻ thông tin bên thứ ba</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Walk/Run (Toggle)</t>
+          <t>Đi/Chạy (Bật/Tắt)</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Lock On Mục tiêu</t>
+          <t>Khóa Mục Tiêu</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Disable Mục tiêu Lock (Giữ)</t>
+          <t>Vô Hiệu Hóa Khóa Mục Tiêu (Giữ)</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Dash/Dodge</t>
+          <t>Lao/Né tránh</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Dash/Dodge</t>
+          <t>Lao/Né tránh</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Công cụ</t>
+          <t>Tiện ích</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Giọng nói Volume</t>
+          <t>Âm lượng giọng nói</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Switch Sang Chế Độ Nhắm</t>
+          <t>Chuyển sang Chế Độ Nhắm</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Sụp Đổ</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Wall Dash</t>
+          <t>Đột Kích Tường</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Pick Up/Interact</t>
+          <t>Nhặt Lên/Tương Tác</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Chuyển sang Nhân vật 1</t>
+          <t>Chuyển sang Nhân Vật 1</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Chuyển sang Nhân vật 2</t>
+          <t>Chuyển sang Nhân Vật 2</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Chuyển sang Nhân vật 3</t>
+          <t>Chuyển sang Nhân Vật 3</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Mail</t>
+          <t>Thư</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Bản đồ</t>
+          <t>Bản Đồ</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Quests</t>
+          <t>Nhiệm vụ</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Đội Setup</t>
+          <t>Thiết lập Đội</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Túi đồ</t>
+          <t>Hành trang</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Resonator Panel</t>
+          <t>Bảng điều khiển Resonator</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Công cụ Wheel</t>
+          <t>Bánh xe tiện ích</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Configure Công cụ</t>
+          <t>Tiện Ích Cấu Hình</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Lựa chọn ngôn ngữ</t>
+          <t>Chọn Ngôn Ngữ</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Lựa chọn ngôn ngữ</t>
+          <t>Chọn Ngôn Ngữ</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Âm lượng hiệu ứng</t>
+          <t>Âm Lượng Hiệu Ứng</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Manage Giọng nói Packs</t>
+          <t>Quản Lý Gói Giọng Nói</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Quyết Tâm</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Brightness</t>
+          <t>Ánh Sáng</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Chất lượng bóng đổ</t>
+          <t>Chất Lượng Bóng</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Special Effects Quality</t>
+          <t>Chất Lượng Hiệu Ứng Đặc Biệt</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>LOD Bias</t>
+          <t>Độ Lệch LOD</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Anti-aliasing</t>
+          <t>Khử răng cưa</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Capsule AO</t>
+          <t>Viên Nang AO</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Trò Chuyện</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Screen Mode</t>
+          <t>Chế Độ Màn Hình</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Theo dõi Nhiệm vụ</t>
+          <t>Nhiệm vụ bản nhạc</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Volumetric Fog</t>
+          <t>Sương Mù Khối</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Volumetric Lighting</t>
+          <t>Ánh Sáng Khối</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Motion Blur</t>
+          <t>Làm mờ chuyển động</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>V-Sync</t>
+          <t>Đồng Bộ V</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Quyết Tâm</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Ambient Volume</t>
+          <t>Âm Lượng Môi Trường</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Interface Volume</t>
+          <t>Âm Lượng Giao Diện</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Graphics Quality</t>
+          <t>Chất lượng Đồ họa</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Instrument Volume</t>
+          <t>Âm lượng nhạc cụ</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Dynamic Range</t>
+          <t>Phạm Vi Động</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Audio API Compatibility Mode</t>
+          <t>Chế độ tương thích API âm thanh</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Audio/Vibration Phản hồi</t>
+          <t>Phản Hồi Âm Thanh/Rung Động</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Spatial Audio</t>
+          <t>Âm Thanh Không Gian</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Sound Output Device</t>
+          <t>Thiết bị phát Âm thanh</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Sound Output Setting</t>
+          <t>Cài đặt Phát Âm thanh</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Crowd Density</t>
+          <t>Mật Độ Đám Đông</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Party Member Effects in Co-op</t>
+          <t>Hiệu ứng thành viên trong Hợp Tác</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Frame Rate</t>
+          <t>Tốc Độ Khung Hình</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>UI Brightness (HDR)</t>
+          <t>Độ sáng UI (HDR)</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>HDR Peak Brightness</t>
+          <t>Độ Sáng Đỉnh HDR</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Device Info</t>
+          <t>Thông tin Thiết bị</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Memory</t>
+          <t>Trí nhớ</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Graphics Card</t>
+          <t>Card Đồ họa</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Video Memory</t>
+          <t>Ký ức Video</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Graphics Driver</t>
+          <t>Trình điều khiển Đồ họa</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Drive Type</t>
+          <t>Loại Xe</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Graphics API</t>
+          <t>API Đồ họa</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Windows Version</t>
+          <t>Phiên bản Windows</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Khó Disk Drive (HDD)</t>
+          <t>Ổ Cứng (HDD)</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Solid-State Drive (SSD)</t>
+          <t>Ổ cứng thể rắn (SSD)</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Frame Generation</t>
+          <t>Tạo Khung Hình</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Super Resolution</t>
+          <t>Siêu Độ Phân Giải</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Sharpening</t>
+          <t>Mài giũa...</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Customize Keybinds</t>
+          <t>Tùy Chỉnh Phím Tắt</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Switch Appearance</t>
+          <t>Thay đổi ngoại hình</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Move Forward</t>
+          <t>Tiến Lên</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Horizontal Camera Sensitivity</t>
+          <t>Độ Nhạy Cảm Ống Kính Ngang</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Move Backwards</t>
+          <t>Lùi</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Vertical Camera Sensitivity</t>
+          <t>Độ Nhạy Camera Dọc</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Horizontal Camera Sensitivity: Aiming</t>
+          <t>Độ Nhạy Cảm Ống Kính Ngang: Ngắm Mục Tiêu</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Vertical Camera Sensitivity: Aiming</t>
+          <t>Độ Nhạy Camera Dọc: Ngắm Mục Tiêu</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Camera Shake Intensity</t>
+          <t>Cường độ rung máy quay</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Regular Camera Distance</t>
+          <t>Khoảng Cách Máy Quay Thường</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Move Left</t>
+          <t>Trái</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>"Trails of Companion Stars" đã bị gỡ bỏ</t>
+          <t>"Đã gỡ bỏ \"Dấu Sao Đồng Hành\""</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>"Trails of Companion Stars" đã được trang bị</t>
+          <t>"Đã trang bị \"Dấu Sao Đồng Hành\""</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Không hỗ trợ Mô phỏng Thời tiết tại khu vực hiện tại</t>
+          <t>Không thể mô phỏng thời tiết tại khu vực này</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Vehicle</t>
+          <t>Phương Tiện Giao Thông</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Công cụ</t>
+          <t>Tiện ích</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Function</t>
+          <t>Chức năng</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Intel XeSS</t>
+          <t>Đồ họa XeSS</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Intel XeSS Graphics</t>
+          <t>Chất lượng Đồ họa XeSS</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>MetalFX</t>
+          <t>Hiệu Ứng Âm Thanh Kim Loại</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Tăng tốc IRX Rendering ở 120 FPS</t>
+          <t>Tăng tốc kết xuất IRX - 120 FPS</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Electro Predator</t>
+          <t>Thú Điện Khát Máu</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Aero Predator</t>
+          <t>Thú Dữ Gió</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Havoc Warrior</t>
+          <t>Chiến Binh Hỗn Loạn</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Whiff Whaff</t>
+          <t>Phì Phò</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Baby Roseshroom</t>
+          <t>Nấm Hồng Bé Nhỏ</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Exile</t>
+          <t>Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Exile</t>
+          <t>Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Exile</t>
+          <t>Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Exile</t>
+          <t>Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Exile</t>
+          <t>Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Exile</t>
+          <t>Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Exile</t>
+          <t>Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Exile</t>
+          <t>Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Exile</t>
+          <t>Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Exile</t>
+          <t>Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Exile</t>
+          <t>Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Exile</t>
+          <t>Kẻ Lưu Đày</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Hooscamp Flinger</t>
+          <t>Quái Hooscamp Ném Vật</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Hooscamp Clapperclaw</t>
+          <t>Quái Hooscamp Ném Đá</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Fractsidus Cannoneer</t>
+          <t>Pháo Thủ Fractsidus</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Fractsidus Gunmaster</t>
+          <t>Bậc Thầy Súng Fractsidus</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Trigram</t>
+          <t>Quẻ</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Yin-Yang Balance</t>
+          <t>Âm Dương Cân Bằng</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Thunder Spell - Heaven, Earth, Mind</t>
+          <t>Phép Lôi - Thiên, Địa, Tâm</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Five Thunders Spell Array</t>
+          <t>Bát Quái Ngũ Lôi Trận</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Lava Larva</t>
+          <t>Ấu trùng dung nham</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Dwarf Cassowary</t>
+          <t>Đà Điểu Lùn</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Golden Junrock</t>
+          <t>Junrock Vàng</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Calcified Junrock</t>
+          <t>Đá Junrock Hóa Thạch</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
